--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/biobio.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -936,6 +936,128 @@
       </c>
       <c r="M8" s="2" t="n">
         <v>41743.24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057543-1517-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.607.201-3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>2671.32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1057417-15577-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>34172.86</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/biobio.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057417-15577-CM26</t>
+          <t>1057543-1528-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,7 +1057,621 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
+        <v>9074.370000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1057417-15577-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>34172.86</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1057417-15864-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>16875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1057417-15578-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3178-3106-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.102.025-2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SPINEX CORPORATION CHILE S.A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>4185.93</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1057417-16269-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>12602.06</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1057417-16268-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>39264.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1057417-16267-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>21599.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1057417-16266-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>20205.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1057417-16829-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>64527.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3178-3061-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.102.025-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>11699.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/biobio.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057543-1517-CM26</t>
+          <t>1057417-14576-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.607.201-3</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2671.32</v>
+        <v>8292.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057543-1528-CM26</t>
+          <t>1057543-1517-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9074.370000000001</v>
+        <v>2671.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057417-15577-CM26</t>
+          <t>1057543-1528-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>34172.86</v>
+        <v>9074.370000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057417-15864-CM26</t>
+          <t>1057417-15577-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>16875</v>
+        <v>34172.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057417-15578-CM26</t>
+          <t>1057417-15864-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3000</v>
+        <v>16875</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3178-3106-CM26</t>
+          <t>1057417-15578-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.102.025-2</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4185.93</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057417-16269-CM26</t>
+          <t>3178-3106-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.102.025-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.166.489-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12602.06</v>
+        <v>4185.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057417-16268-CM26</t>
+          <t>1057417-16269-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>39264.2</v>
+        <v>12602.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057417-16267-CM26</t>
+          <t>1057417-16268-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21599.84</v>
+        <v>39264.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057417-16266-CM26</t>
+          <t>1057417-16267-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>20205.85</v>
+        <v>21599.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057417-16829-CM26</t>
+          <t>1057417-16266-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1591,86 +1591,147 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>64527.95</v>
+        <v>20205.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>1057417-16829-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>64527.95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>3178-3061-CM26</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>61.102.025-2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>76.825.774-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
         <v>11699.83</v>
       </c>
     </row>
